--- a/sources/table_normalization/xlsx/environment-table14.xlsx
+++ b/sources/table_normalization/xlsx/environment-table14.xlsx
@@ -1113,10 +1113,6 @@
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1160,14 +1156,15 @@
     <xf numFmtId="165" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1177,15 +1174,18 @@
     <xf numFmtId="165" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -10008,305 +10008,305 @@
       <c r="A4" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="73" t="s">
+      <c r="B4" s="79" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
-      <c r="Q4" s="75"/>
-      <c r="R4" s="74"/>
-      <c r="S4" s="74"/>
-      <c r="T4" s="75"/>
-      <c r="U4" s="74"/>
-      <c r="V4" s="74"/>
-      <c r="W4" s="75"/>
-      <c r="X4" s="74"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="73" t="s">
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="80"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="80"/>
+      <c r="Y4" s="82"/>
+      <c r="Z4" s="79" t="s">
         <v>166</v>
       </c>
-      <c r="AA4" s="74"/>
-      <c r="AB4" s="74"/>
-      <c r="AC4" s="75"/>
-      <c r="AD4" s="74"/>
-      <c r="AE4" s="74"/>
-      <c r="AF4" s="75"/>
-      <c r="AG4" s="74"/>
-      <c r="AH4" s="74"/>
-      <c r="AI4" s="75"/>
-      <c r="AJ4" s="74"/>
-      <c r="AK4" s="74"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="74"/>
-      <c r="AN4" s="74"/>
-      <c r="AO4" s="75"/>
-      <c r="AP4" s="74"/>
-      <c r="AQ4" s="74"/>
-      <c r="AR4" s="75"/>
-      <c r="AS4" s="74"/>
-      <c r="AT4" s="74"/>
-      <c r="AU4" s="75"/>
-      <c r="AV4" s="74"/>
-      <c r="AW4" s="74"/>
-      <c r="AX4" s="75"/>
-      <c r="AY4" s="74"/>
-      <c r="AZ4" s="74"/>
-      <c r="BA4" s="75"/>
-      <c r="BB4" s="74"/>
-      <c r="BC4" s="74"/>
-      <c r="BD4" s="75"/>
-      <c r="BE4" s="74"/>
-      <c r="BF4" s="74"/>
-      <c r="BG4" s="75"/>
-      <c r="BH4" s="74"/>
-      <c r="BI4" s="74"/>
-      <c r="BJ4" s="75"/>
-      <c r="BK4" s="74"/>
-      <c r="BL4" s="74"/>
-      <c r="BM4" s="75"/>
-      <c r="BN4" s="74"/>
-      <c r="BO4" s="76"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="80"/>
+      <c r="AC4" s="81"/>
+      <c r="AD4" s="80"/>
+      <c r="AE4" s="80"/>
+      <c r="AF4" s="81"/>
+      <c r="AG4" s="80"/>
+      <c r="AH4" s="80"/>
+      <c r="AI4" s="81"/>
+      <c r="AJ4" s="80"/>
+      <c r="AK4" s="80"/>
+      <c r="AL4" s="81"/>
+      <c r="AM4" s="80"/>
+      <c r="AN4" s="80"/>
+      <c r="AO4" s="81"/>
+      <c r="AP4" s="80"/>
+      <c r="AQ4" s="80"/>
+      <c r="AR4" s="81"/>
+      <c r="AS4" s="80"/>
+      <c r="AT4" s="80"/>
+      <c r="AU4" s="81"/>
+      <c r="AV4" s="80"/>
+      <c r="AW4" s="80"/>
+      <c r="AX4" s="81"/>
+      <c r="AY4" s="80"/>
+      <c r="AZ4" s="80"/>
+      <c r="BA4" s="81"/>
+      <c r="BB4" s="80"/>
+      <c r="BC4" s="80"/>
+      <c r="BD4" s="81"/>
+      <c r="BE4" s="80"/>
+      <c r="BF4" s="80"/>
+      <c r="BG4" s="81"/>
+      <c r="BH4" s="80"/>
+      <c r="BI4" s="80"/>
+      <c r="BJ4" s="81"/>
+      <c r="BK4" s="80"/>
+      <c r="BL4" s="80"/>
+      <c r="BM4" s="81"/>
+      <c r="BN4" s="80"/>
+      <c r="BO4" s="82"/>
     </row>
     <row r="5" spans="1:67" s="3" customFormat="1" ht="32.25" customHeight="1">
-      <c r="A5" s="55"/>
-      <c r="B5" s="77" t="s">
+      <c r="A5" s="77"/>
+      <c r="B5" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="78"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="77" t="s">
+      <c r="C5" s="75"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="78"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="77" t="s">
+      <c r="F5" s="75"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="78"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="77" t="s">
+      <c r="I5" s="75"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="L5" s="78"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="77" t="s">
+      <c r="L5" s="75"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="78"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="77" t="s">
+      <c r="O5" s="75"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="R5" s="78"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="77" t="s">
+      <c r="R5" s="75"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="U5" s="78"/>
-      <c r="V5" s="79"/>
-      <c r="W5" s="77" t="s">
+      <c r="U5" s="75"/>
+      <c r="V5" s="76"/>
+      <c r="W5" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="X5" s="78"/>
-      <c r="Y5" s="79"/>
-      <c r="Z5" s="80" t="s">
+      <c r="X5" s="75"/>
+      <c r="Y5" s="76"/>
+      <c r="Z5" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="AA5" s="81"/>
-      <c r="AB5" s="82"/>
-      <c r="AC5" s="80" t="s">
+      <c r="AA5" s="72"/>
+      <c r="AB5" s="73"/>
+      <c r="AC5" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="AD5" s="81"/>
-      <c r="AE5" s="82"/>
-      <c r="AF5" s="80" t="s">
+      <c r="AD5" s="72"/>
+      <c r="AE5" s="73"/>
+      <c r="AF5" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="AG5" s="81"/>
-      <c r="AH5" s="82"/>
-      <c r="AI5" s="80" t="s">
+      <c r="AG5" s="72"/>
+      <c r="AH5" s="73"/>
+      <c r="AI5" s="71" t="s">
         <v>15</v>
       </c>
-      <c r="AJ5" s="81"/>
-      <c r="AK5" s="81"/>
-      <c r="AL5" s="80" t="s">
+      <c r="AJ5" s="72"/>
+      <c r="AK5" s="72"/>
+      <c r="AL5" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="AM5" s="81"/>
-      <c r="AN5" s="82"/>
-      <c r="AO5" s="80" t="s">
+      <c r="AM5" s="72"/>
+      <c r="AN5" s="73"/>
+      <c r="AO5" s="71" t="s">
         <v>17</v>
       </c>
-      <c r="AP5" s="81"/>
-      <c r="AQ5" s="82"/>
-      <c r="AR5" s="80" t="s">
+      <c r="AP5" s="72"/>
+      <c r="AQ5" s="73"/>
+      <c r="AR5" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="81"/>
-      <c r="AT5" s="81"/>
-      <c r="AU5" s="80" t="s">
+      <c r="AS5" s="72"/>
+      <c r="AT5" s="72"/>
+      <c r="AU5" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="AV5" s="81"/>
-      <c r="AW5" s="82"/>
-      <c r="AX5" s="80" t="s">
+      <c r="AV5" s="72"/>
+      <c r="AW5" s="73"/>
+      <c r="AX5" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="AY5" s="81"/>
-      <c r="AZ5" s="82"/>
-      <c r="BA5" s="80" t="s">
+      <c r="AY5" s="72"/>
+      <c r="AZ5" s="73"/>
+      <c r="BA5" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="BB5" s="81"/>
-      <c r="BC5" s="82"/>
-      <c r="BD5" s="80" t="s">
+      <c r="BB5" s="72"/>
+      <c r="BC5" s="73"/>
+      <c r="BD5" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="BE5" s="81"/>
-      <c r="BF5" s="82"/>
-      <c r="BG5" s="80" t="s">
+      <c r="BE5" s="72"/>
+      <c r="BF5" s="73"/>
+      <c r="BG5" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="BH5" s="81"/>
-      <c r="BI5" s="82"/>
-      <c r="BJ5" s="80" t="s">
+      <c r="BH5" s="72"/>
+      <c r="BI5" s="73"/>
+      <c r="BJ5" s="71" t="s">
         <v>24</v>
       </c>
-      <c r="BK5" s="81"/>
-      <c r="BL5" s="81"/>
-      <c r="BM5" s="80" t="s">
+      <c r="BK5" s="72"/>
+      <c r="BL5" s="72"/>
+      <c r="BM5" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="BN5" s="81"/>
-      <c r="BO5" s="82"/>
+      <c r="BN5" s="72"/>
+      <c r="BO5" s="73"/>
     </row>
     <row r="6" spans="1:67" s="1" customFormat="1">
-      <c r="A6" s="56"/>
-      <c r="B6" s="70"/>
-      <c r="C6" s="68" t="s">
+      <c r="A6" s="78"/>
+      <c r="B6" s="68"/>
+      <c r="C6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="69"/>
-      <c r="E6" s="70"/>
-      <c r="F6" s="68" t="s">
+      <c r="D6" s="67"/>
+      <c r="E6" s="68"/>
+      <c r="F6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="69"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="68" t="s">
+      <c r="G6" s="67"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="69"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="68" t="s">
+      <c r="J6" s="67"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="M6" s="69"/>
-      <c r="N6" s="70"/>
-      <c r="O6" s="68" t="s">
+      <c r="M6" s="67"/>
+      <c r="N6" s="68"/>
+      <c r="O6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="69"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="68" t="s">
+      <c r="P6" s="67"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="S6" s="69"/>
-      <c r="T6" s="70"/>
-      <c r="U6" s="68" t="s">
+      <c r="S6" s="67"/>
+      <c r="T6" s="68"/>
+      <c r="U6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="V6" s="69"/>
-      <c r="W6" s="70"/>
-      <c r="X6" s="68" t="s">
+      <c r="V6" s="67"/>
+      <c r="W6" s="68"/>
+      <c r="X6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="Y6" s="69"/>
-      <c r="Z6" s="70"/>
-      <c r="AA6" s="68" t="s">
+      <c r="Y6" s="67"/>
+      <c r="Z6" s="68"/>
+      <c r="AA6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="70"/>
-      <c r="AD6" s="68" t="s">
+      <c r="AB6" s="67"/>
+      <c r="AC6" s="68"/>
+      <c r="AD6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AE6" s="69"/>
-      <c r="AF6" s="70"/>
-      <c r="AG6" s="68" t="s">
+      <c r="AE6" s="67"/>
+      <c r="AF6" s="68"/>
+      <c r="AG6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AH6" s="69"/>
-      <c r="AI6" s="70"/>
-      <c r="AJ6" s="68" t="s">
+      <c r="AH6" s="67"/>
+      <c r="AI6" s="68"/>
+      <c r="AJ6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AK6" s="71"/>
-      <c r="AL6" s="70"/>
-      <c r="AM6" s="68" t="s">
+      <c r="AK6" s="69"/>
+      <c r="AL6" s="68"/>
+      <c r="AM6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AN6" s="69"/>
-      <c r="AO6" s="70"/>
-      <c r="AP6" s="68" t="s">
+      <c r="AN6" s="67"/>
+      <c r="AO6" s="68"/>
+      <c r="AP6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AQ6" s="69"/>
-      <c r="AR6" s="70"/>
-      <c r="AS6" s="68" t="s">
+      <c r="AQ6" s="67"/>
+      <c r="AR6" s="68"/>
+      <c r="AS6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AT6" s="71"/>
-      <c r="AU6" s="70"/>
-      <c r="AV6" s="68" t="s">
+      <c r="AT6" s="69"/>
+      <c r="AU6" s="68"/>
+      <c r="AV6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AW6" s="69"/>
-      <c r="AX6" s="70"/>
-      <c r="AY6" s="68" t="s">
+      <c r="AW6" s="67"/>
+      <c r="AX6" s="68"/>
+      <c r="AY6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="AZ6" s="69"/>
-      <c r="BA6" s="70"/>
-      <c r="BB6" s="68" t="s">
+      <c r="AZ6" s="67"/>
+      <c r="BA6" s="68"/>
+      <c r="BB6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="BC6" s="69"/>
-      <c r="BD6" s="70"/>
-      <c r="BE6" s="68" t="s">
+      <c r="BC6" s="67"/>
+      <c r="BD6" s="68"/>
+      <c r="BE6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="BF6" s="69"/>
-      <c r="BG6" s="70"/>
-      <c r="BH6" s="68" t="s">
+      <c r="BF6" s="67"/>
+      <c r="BG6" s="68"/>
+      <c r="BH6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="BI6" s="69"/>
-      <c r="BJ6" s="70"/>
-      <c r="BK6" s="68" t="s">
+      <c r="BI6" s="67"/>
+      <c r="BJ6" s="68"/>
+      <c r="BK6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="BL6" s="71"/>
-      <c r="BM6" s="70"/>
-      <c r="BN6" s="68" t="s">
+      <c r="BL6" s="69"/>
+      <c r="BM6" s="68"/>
+      <c r="BN6" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="BO6" s="69"/>
+      <c r="BO6" s="67"/>
     </row>
     <row r="7" spans="1:67" s="1" customFormat="1">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="55" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="8">
@@ -10315,7 +10315,7 @@
       <c r="C7" s="9">
         <v>2008</v>
       </c>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="8">
@@ -10324,7 +10324,7 @@
       <c r="F7" s="9">
         <v>2008</v>
       </c>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="H7" s="8">
@@ -10333,7 +10333,7 @@
       <c r="I7" s="9">
         <v>2008</v>
       </c>
-      <c r="J7" s="72" t="s">
+      <c r="J7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="K7" s="8">
@@ -10342,7 +10342,7 @@
       <c r="L7" s="9">
         <v>2008</v>
       </c>
-      <c r="M7" s="72" t="s">
+      <c r="M7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="N7" s="8">
@@ -10351,7 +10351,7 @@
       <c r="O7" s="9">
         <v>2008</v>
       </c>
-      <c r="P7" s="72" t="s">
+      <c r="P7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="Q7" s="8">
@@ -10360,7 +10360,7 @@
       <c r="R7" s="9">
         <v>2008</v>
       </c>
-      <c r="S7" s="72" t="s">
+      <c r="S7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="T7" s="8">
@@ -10369,7 +10369,7 @@
       <c r="U7" s="9">
         <v>2008</v>
       </c>
-      <c r="V7" s="72" t="s">
+      <c r="V7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="W7" s="8">
@@ -10378,7 +10378,7 @@
       <c r="X7" s="9">
         <v>2008</v>
       </c>
-      <c r="Y7" s="72" t="s">
+      <c r="Y7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="Z7" s="19">
@@ -10387,7 +10387,7 @@
       <c r="AA7" s="20">
         <v>2008</v>
       </c>
-      <c r="AB7" s="72" t="s">
+      <c r="AB7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="AC7" s="19">
@@ -10396,7 +10396,7 @@
       <c r="AD7" s="20">
         <v>2008</v>
       </c>
-      <c r="AE7" s="72" t="s">
+      <c r="AE7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="AF7" s="19">
@@ -10405,7 +10405,7 @@
       <c r="AG7" s="20">
         <v>2008</v>
       </c>
-      <c r="AH7" s="72" t="s">
+      <c r="AH7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="AI7" s="19">
@@ -10414,7 +10414,7 @@
       <c r="AJ7" s="20">
         <v>2008</v>
       </c>
-      <c r="AK7" s="68" t="s">
+      <c r="AK7" s="66" t="s">
         <v>28</v>
       </c>
       <c r="AL7" s="30">
@@ -10423,7 +10423,7 @@
       <c r="AM7" s="20">
         <v>2008</v>
       </c>
-      <c r="AN7" s="72" t="s">
+      <c r="AN7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="AO7" s="19">
@@ -10432,7 +10432,7 @@
       <c r="AP7" s="20">
         <v>2008</v>
       </c>
-      <c r="AQ7" s="72" t="s">
+      <c r="AQ7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="AR7" s="19">
@@ -10441,7 +10441,7 @@
       <c r="AS7" s="20">
         <v>2008</v>
       </c>
-      <c r="AT7" s="68" t="s">
+      <c r="AT7" s="66" t="s">
         <v>28</v>
       </c>
       <c r="AU7" s="19">
@@ -10450,7 +10450,7 @@
       <c r="AV7" s="20">
         <v>2008</v>
       </c>
-      <c r="AW7" s="72" t="s">
+      <c r="AW7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="AX7" s="19">
@@ -10459,7 +10459,7 @@
       <c r="AY7" s="20">
         <v>2008</v>
       </c>
-      <c r="AZ7" s="72" t="s">
+      <c r="AZ7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="BA7" s="19">
@@ -10468,7 +10468,7 @@
       <c r="BB7" s="20">
         <v>2008</v>
       </c>
-      <c r="BC7" s="72" t="s">
+      <c r="BC7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="BD7" s="19">
@@ -10477,7 +10477,7 @@
       <c r="BE7" s="20">
         <v>2008</v>
       </c>
-      <c r="BF7" s="72" t="s">
+      <c r="BF7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="BG7" s="19">
@@ -10486,7 +10486,7 @@
       <c r="BH7" s="20">
         <v>2008</v>
       </c>
-      <c r="BI7" s="72" t="s">
+      <c r="BI7" s="70" t="s">
         <v>28</v>
       </c>
       <c r="BJ7" s="19">
@@ -10495,7 +10495,7 @@
       <c r="BK7" s="20">
         <v>2008</v>
       </c>
-      <c r="BL7" s="68" t="s">
+      <c r="BL7" s="66" t="s">
         <v>28</v>
       </c>
       <c r="BM7" s="19">
@@ -10504,7 +10504,7 @@
       <c r="BN7" s="20">
         <v>2008</v>
       </c>
-      <c r="BO7" s="72" t="s">
+      <c r="BO7" s="70" t="s">
         <v>28</v>
       </c>
     </row>
@@ -31767,32 +31767,32 @@
       </c>
     </row>
     <row r="118" spans="1:67" s="1" customFormat="1">
-      <c r="A118" s="58" t="s">
+      <c r="A118" s="56" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="119" spans="1:67" s="1" customFormat="1">
-      <c r="A119" s="59" t="s">
+      <c r="A119" s="57" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="120" spans="1:67" s="1" customFormat="1">
-      <c r="A120" s="60" t="s">
+      <c r="A120" s="58" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="121" spans="1:67" s="1" customFormat="1">
-      <c r="A121" s="61" t="s">
+      <c r="A121" s="59" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="122" spans="1:67" s="1" customFormat="1">
-      <c r="A122" s="61" t="s">
+      <c r="A122" s="59" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="123" spans="1:67" s="1" customFormat="1">
-      <c r="A123" s="62" t="s">
+      <c r="A123" s="60" t="s">
         <v>138</v>
       </c>
     </row>
@@ -31800,47 +31800,47 @@
       <c r="A124" s="40"/>
     </row>
     <row r="125" spans="1:67" s="1" customFormat="1">
-      <c r="A125" s="61" t="s">
+      <c r="A125" s="59" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="126" spans="1:67">
-      <c r="A126" s="63" t="s">
+      <c r="A126" s="61" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="127" spans="1:67">
-      <c r="A127" s="63" t="s">
+      <c r="A127" s="61" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:67">
-      <c r="A128" s="59" t="s">
+      <c r="A128" s="57" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="129" spans="1:1">
-      <c r="A129" s="59" t="s">
+      <c r="A129" s="57" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="59" t="s">
+      <c r="A130" s="57" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="131" spans="1:1">
-      <c r="A131" s="59" t="s">
+      <c r="A131" s="57" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="59" t="s">
+      <c r="A132" s="57" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="59" t="s">
+      <c r="A133" s="57" t="s">
         <v>147</v>
       </c>
     </row>
@@ -31851,62 +31851,62 @@
       <c r="A135" s="46"/>
     </row>
     <row r="136" spans="1:1">
-      <c r="A136" s="59" t="s">
+      <c r="A136" s="57" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="137" spans="1:1">
-      <c r="A137" s="59" t="s">
+      <c r="A137" s="57" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="138" spans="1:1">
-      <c r="A138" s="59" t="s">
+      <c r="A138" s="57" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="139" spans="1:1">
-      <c r="A139" s="59" t="s">
+      <c r="A139" s="57" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="140" spans="1:1">
-      <c r="A140" s="59" t="s">
+      <c r="A140" s="57" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="142" spans="1:1">
-      <c r="A142" s="59" t="s">
+      <c r="A142" s="57" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="143" spans="1:1">
-      <c r="A143" s="59" t="s">
+      <c r="A143" s="57" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="144" spans="1:1">
-      <c r="A144" s="59" t="s">
+      <c r="A144" s="57" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="145" spans="1:67">
-      <c r="A145" s="59" t="s">
+      <c r="A145" s="57" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="146" spans="1:67">
-      <c r="A146" s="59" t="s">
+      <c r="A146" s="57" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="147" spans="1:67">
-      <c r="A147" s="59" t="s">
+      <c r="A147" s="57" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="149" spans="1:67">
-      <c r="A149" s="64" t="s">
+      <c r="A149" s="62" t="s">
         <v>159</v>
       </c>
       <c r="Z149" s="6"/>
@@ -31953,7 +31953,7 @@
       <c r="BO149" s="6"/>
     </row>
     <row r="150" spans="1:67">
-      <c r="A150" s="65" t="s">
+      <c r="A150" s="63" t="s">
         <v>160</v>
       </c>
       <c r="Z150" s="6"/>
@@ -32000,7 +32000,7 @@
       <c r="BO150" s="6"/>
     </row>
     <row r="151" spans="1:67">
-      <c r="A151" s="65" t="s">
+      <c r="A151" s="63" t="s">
         <v>161</v>
       </c>
       <c r="Z151" s="6"/>
@@ -32047,7 +32047,7 @@
       <c r="BO151" s="6"/>
     </row>
     <row r="152" spans="1:67">
-      <c r="A152" s="65" t="s">
+      <c r="A152" s="63" t="s">
         <v>162</v>
       </c>
       <c r="Z152" s="6"/>
@@ -32094,7 +32094,7 @@
       <c r="BO152" s="6"/>
     </row>
     <row r="153" spans="1:67">
-      <c r="A153" s="65" t="s">
+      <c r="A153" s="63" t="s">
         <v>163</v>
       </c>
       <c r="Z153" s="6"/>
@@ -32141,7 +32141,7 @@
       <c r="BO153" s="6"/>
     </row>
     <row r="154" spans="1:67">
-      <c r="A154" s="66" t="s">
+      <c r="A154" s="64" t="s">
         <v>164</v>
       </c>
       <c r="Z154" s="6"/>
@@ -32233,7 +32233,7 @@
       <c r="BO155" s="6"/>
     </row>
     <row r="156" spans="1:67">
-      <c r="A156" s="67" t="s">
+      <c r="A156" s="65" t="s">
         <v>165</v>
       </c>
       <c r="Z156" s="6"/>
@@ -32282,6 +32282,21 @@
   </sheetData>
   <autoFilter ref="A7:A123"/>
   <mergeCells count="22">
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="N5:P5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="W5:Y5"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="AC5:AE5"/>
+    <mergeCell ref="AF5:AH5"/>
+    <mergeCell ref="AI5:AK5"/>
+    <mergeCell ref="AL5:AN5"/>
+    <mergeCell ref="AO5:AQ5"/>
+    <mergeCell ref="AR5:AT5"/>
     <mergeCell ref="BJ5:BL5"/>
     <mergeCell ref="BM5:BO5"/>
     <mergeCell ref="AU5:AW5"/>
@@ -32289,21 +32304,6 @@
     <mergeCell ref="BA5:BC5"/>
     <mergeCell ref="BD5:BF5"/>
     <mergeCell ref="BG5:BI5"/>
-    <mergeCell ref="AF5:AH5"/>
-    <mergeCell ref="AI5:AK5"/>
-    <mergeCell ref="AL5:AN5"/>
-    <mergeCell ref="AO5:AQ5"/>
-    <mergeCell ref="AR5:AT5"/>
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="T5:V5"/>
-    <mergeCell ref="W5:Y5"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="AC5:AE5"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="N5:P5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1"/>
